--- a/data/dividends_info_20260504.xlsx
+++ b/data/dividends_info_20260504.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.98500061035156</v>
+        <v>47.00500106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1875586096805941</v>
+        <v>0.1914689883095215</v>
       </c>
       <c r="J2" t="n">
         <v>315</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.75</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.255605381165919</v>
+        <v>1.291512896949333</v>
       </c>
       <c r="J3" t="n">
         <v>294</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.5</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6224066168375152</v>
       </c>
       <c r="J4" t="n">
         <v>224</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.98500061035156</v>
+        <v>47.00500106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1875586096805941</v>
+        <v>0.1914689883095215</v>
       </c>
       <c r="J6" t="n">
         <v>224</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>203</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.889999866485596</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I8" t="n">
-        <v>3.395585815510971</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J8" t="n">
         <v>196</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.25</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.96</v>
+        <v>0.9756097409688789</v>
       </c>
       <c r="J9" t="n">
         <v>168</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.960000038146973</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J11" t="n">
         <v>147</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>47.98500061035156</v>
+        <v>47.00500106811523</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1875586096805941</v>
+        <v>0.1914689883095215</v>
       </c>
       <c r="J12" t="n">
         <v>140</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.960000038146973</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J14" t="n">
         <v>91</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.010000228881836</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I15" t="n">
-        <v>4.159733618621054</v>
+        <v>4.187604837285504</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.644000053405762</v>
+        <v>9.673999786376953</v>
       </c>
       <c r="I16" t="n">
-        <v>2.695976758193624</v>
+        <v>2.687616350437957</v>
       </c>
       <c r="J16" t="n">
         <v>77</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16.28000068664551</v>
+        <v>15.76000022888184</v>
       </c>
       <c r="I17" t="n">
-        <v>3.68550353005931</v>
+        <v>3.807106543694319</v>
       </c>
       <c r="J17" t="n">
         <v>77</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.733999967575073</v>
+        <v>3.674000024795532</v>
       </c>
       <c r="I18" t="n">
-        <v>5.891805085977865</v>
+        <v>5.988023911683114</v>
       </c>
       <c r="J18" t="n">
         <v>77</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.824999809265137</v>
+        <v>5.815000057220459</v>
       </c>
       <c r="I20" t="n">
-        <v>1.716738253638083</v>
+        <v>1.719690438795963</v>
       </c>
       <c r="J20" t="n">
         <v>77</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.570000171661377</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="I22" t="n">
-        <v>2.154398497338059</v>
+        <v>2.177858348734625</v>
       </c>
       <c r="J22" t="n">
         <v>70</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9.5</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5376343975757395</v>
       </c>
       <c r="J23" t="n">
         <v>70</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.139999866485596</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="I25" t="n">
-        <v>1.690821310567391</v>
+        <v>1.728394980329585</v>
       </c>
       <c r="J25" t="n">
         <v>63</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.70000076293945</v>
+        <v>34.20000076293945</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4322766475561697</v>
+        <v>0.4385964814437848</v>
       </c>
       <c r="J26" t="n">
         <v>63</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.900000095367432</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6779660907362907</v>
+        <v>0.6722689291134659</v>
       </c>
       <c r="J27" t="n">
         <v>56</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22.07999992370605</v>
+        <v>22.23999977111816</v>
       </c>
       <c r="I28" t="n">
-        <v>1.132246380723892</v>
+        <v>1.124100730993086</v>
       </c>
       <c r="J28" t="n">
         <v>49</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>26.45000076293945</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7372400543489783</v>
+        <v>0.7471264258618348</v>
       </c>
       <c r="J29" t="n">
         <v>49</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.904999971389771</v>
+        <v>1.995000004768372</v>
       </c>
       <c r="I30" t="n">
-        <v>1.732283490583217</v>
+        <v>1.654135334392214</v>
       </c>
       <c r="J30" t="n">
         <v>49</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.874000072479248</v>
+        <v>4.935999870300293</v>
       </c>
       <c r="I31" t="n">
-        <v>5.949938360433513</v>
+        <v>5.875202747571328</v>
       </c>
       <c r="J31" t="n">
         <v>49</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.95799994468689</v>
+        <v>3.924000024795532</v>
       </c>
       <c r="I32" t="n">
-        <v>4.04244573612942</v>
+        <v>4.077471941614911</v>
       </c>
       <c r="J32" t="n">
         <v>49</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.565999984741211</v>
+        <v>2.555999994277954</v>
       </c>
       <c r="I33" t="n">
-        <v>5.401402993927852</v>
+        <v>5.422535223406884</v>
       </c>
       <c r="J33" t="n">
         <v>49</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>53.2599983215332</v>
+        <v>52.77999877929688</v>
       </c>
       <c r="I34" t="n">
-        <v>1.18287649240366</v>
+        <v>1.193633979861173</v>
       </c>
       <c r="J34" t="n">
         <v>49</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.034999847412109</v>
+        <v>4.978000164031982</v>
       </c>
       <c r="I35" t="n">
-        <v>2.780536330541445</v>
+        <v>2.812374354897682</v>
       </c>
       <c r="J35" t="n">
         <v>49</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.45000076293945</v>
+        <v>19.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4.010282619043556</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>49</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>22.32999992370605</v>
+        <v>22.07999992370605</v>
       </c>
       <c r="I37" t="n">
-        <v>3.806538302302545</v>
+        <v>3.849637694461234</v>
       </c>
       <c r="J37" t="n">
         <v>49</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47.98500061035156</v>
+        <v>47.00500106811523</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1875586096805941</v>
+        <v>0.1914689883095215</v>
       </c>
       <c r="J38" t="n">
         <v>49</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6.578000068664551</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="I39" t="n">
-        <v>2.756156857821485</v>
+        <v>2.759512865494402</v>
       </c>
       <c r="J39" t="n">
         <v>49</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8.649999618530273</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I40" t="n">
-        <v>3.005780479377371</v>
+        <v>3.044496500718773</v>
       </c>
       <c r="J40" t="n">
         <v>49</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.03999996185303</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I41" t="n">
-        <v>2.758964153908977</v>
+        <v>2.742574153840692</v>
       </c>
       <c r="J41" t="n">
         <v>49</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.154999971389771</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="I42" t="n">
-        <v>1.168831197784008</v>
+        <v>1.184210541175673</v>
       </c>
       <c r="J42" t="n">
         <v>42</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.01200008392334</v>
+        <v>3.956000089645386</v>
       </c>
       <c r="I43" t="n">
-        <v>2.741774618619421</v>
+        <v>2.780586387950774</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.325000047683716</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>4.812030006178806</v>
+        <v>4.804804914888146</v>
       </c>
       <c r="J45" t="n">
         <v>35</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.925000011920929</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="I46" t="n">
-        <v>2.702702667871647</v>
+        <v>2.71739125505287</v>
       </c>
       <c r="J46" t="n">
         <v>35</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>27.70000076293945</v>
+        <v>27.5</v>
       </c>
       <c r="I47" t="n">
-        <v>4.007220106235873</v>
+        <v>4.036363636363636</v>
       </c>
       <c r="J47" t="n">
         <v>31</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9079999923706055</v>
+        <v>0.9089999794960022</v>
       </c>
       <c r="I48" t="n">
-        <v>3.30396478547054</v>
+        <v>3.300330107447702</v>
       </c>
       <c r="J48" t="n">
         <v>28</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5080000162124634</v>
       </c>
       <c r="I49" t="n">
-        <v>4.509804005899691</v>
+        <v>4.527558910624245</v>
       </c>
       <c r="J49" t="n">
         <v>28</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>19.25</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="I50" t="n">
-        <v>3.116883116883117</v>
+        <v>3.084832783879659</v>
       </c>
       <c r="J50" t="n">
         <v>28</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8.899999618530273</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I53" t="n">
-        <v>3.370786661331805</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J53" t="n">
         <v>21</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.25</v>
+        <v>13.34000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>1.886792452830189</v>
+        <v>1.874062947079512</v>
       </c>
       <c r="J54" t="n">
         <v>21</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.380000114440918</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8875739344453326</v>
+        <v>0.8955224135533352</v>
       </c>
       <c r="J55" t="n">
         <v>21</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.819999933242798</v>
+        <v>3.809999942779541</v>
       </c>
       <c r="I56" t="n">
-        <v>3.926701639302517</v>
+        <v>3.937007933143675</v>
       </c>
       <c r="J56" t="n">
         <v>21</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13.69999980926514</v>
+        <v>13.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4.233576701276691</v>
+        <v>4.296296296296296</v>
       </c>
       <c r="J57" t="n">
         <v>21</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9.449999809265137</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="I59" t="n">
-        <v>3.068783130722109</v>
+        <v>3.039832297270482</v>
       </c>
       <c r="J59" t="n">
         <v>14</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.069999933242798</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I60" t="n">
-        <v>3.719806883248261</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J60" t="n">
         <v>14</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37.88000106811523</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="I61" t="n">
-        <v>4.329461335154075</v>
+        <v>4.385026559063649</v>
       </c>
       <c r="J61" t="n">
         <v>14</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36.09000015258789</v>
+        <v>35.5099983215332</v>
       </c>
       <c r="I62" t="n">
-        <v>5.541701278869589</v>
+        <v>5.632216543325499</v>
       </c>
       <c r="J62" t="n">
         <v>14</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.936000108718872</v>
+        <v>3.871999979019165</v>
       </c>
       <c r="I63" t="n">
-        <v>2.540650336327074</v>
+        <v>2.582644642093503</v>
       </c>
       <c r="J63" t="n">
         <v>14</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>32.02999877929688</v>
+        <v>31.20999908447266</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4635029836340787</v>
+        <v>0.4756808854693643</v>
       </c>
       <c r="J64" t="n">
         <v>14</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>23.26000022888184</v>
+        <v>23.04000091552734</v>
       </c>
       <c r="I65" t="n">
-        <v>3.955288009230715</v>
+        <v>3.99305539688579</v>
       </c>
       <c r="J65" t="n">
         <v>14</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>8.055000305175781</v>
+        <v>7.989999771118164</v>
       </c>
       <c r="I66" t="n">
-        <v>3.724394644743011</v>
+        <v>3.754693474265473</v>
       </c>
       <c r="J66" t="n">
         <v>14</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>83.09999847412109</v>
+        <v>82.55999755859375</v>
       </c>
       <c r="I67" t="n">
-        <v>1.251504234773092</v>
+        <v>1.259689959731286</v>
       </c>
       <c r="J67" t="n">
         <v>14</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>46.84000015258789</v>
+        <v>45.56000137329102</v>
       </c>
       <c r="I68" t="n">
-        <v>1.494449183859205</v>
+        <v>1.536435423398311</v>
       </c>
       <c r="J68" t="n">
         <v>14</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>55.75</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="I69" t="n">
-        <v>3.946188340807175</v>
+        <v>4.059040533269333</v>
       </c>
       <c r="J69" t="n">
         <v>14</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>9.065999984741211</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I70" t="n">
-        <v>9.485991632996333</v>
+        <v>9.662921762484508</v>
       </c>
       <c r="J70" t="n">
         <v>14</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>12.48200035095215</v>
+        <v>12.35200023651123</v>
       </c>
       <c r="I71" t="n">
-        <v>4.486460376980219</v>
+        <v>4.533678669667591</v>
       </c>
       <c r="J71" t="n">
         <v>14</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2.180000066757202</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I72" t="n">
-        <v>1.834862329132901</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J72" t="n">
         <v>14</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>9.890000343322754</v>
+        <v>9.770000457763672</v>
       </c>
       <c r="I73" t="n">
-        <v>3.03336693211083</v>
+        <v>3.070624216415535</v>
       </c>
       <c r="J73" t="n">
         <v>14</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2.200000047683716</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I74" t="n">
-        <v>4.909090802689231</v>
+        <v>4.976958350363231</v>
       </c>
       <c r="J74" t="n">
         <v>14</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>81.59999847412109</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="I75" t="n">
-        <v>2.524509851128632</v>
+        <v>2.506082818101677</v>
       </c>
       <c r="J75" t="n">
         <v>14</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>14.97999954223633</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="I76" t="n">
-        <v>5.006675720418842</v>
+        <v>5.026809625769762</v>
       </c>
       <c r="J76" t="n">
         <v>14</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.30000019073486</v>
+        <v>14.9399995803833</v>
       </c>
       <c r="I77" t="n">
-        <v>1.960784289281704</v>
+        <v>2.008032184913242</v>
       </c>
       <c r="J77" t="n">
         <v>14</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>46.20000076293945</v>
+        <v>45.59999847412109</v>
       </c>
       <c r="I78" t="n">
-        <v>1.839826809444232</v>
+        <v>1.864035150094121</v>
       </c>
       <c r="J78" t="n">
         <v>14</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>33.20000076293945</v>
+        <v>33.15999984741211</v>
       </c>
       <c r="I79" t="n">
-        <v>2.560240905020819</v>
+        <v>2.563329324219934</v>
       </c>
       <c r="J79" t="n">
         <v>14</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>59.36000061035156</v>
+        <v>59.5</v>
       </c>
       <c r="I80" t="n">
-        <v>2.190026931659597</v>
+        <v>2.184873949579832</v>
       </c>
       <c r="J80" t="n">
         <v>14</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8.079999923706055</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="I81" t="n">
-        <v>7.425742644373663</v>
+        <v>7.389162665717064</v>
       </c>
       <c r="J81" t="n">
         <v>14</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6.050000190734863</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I82" t="n">
-        <v>7.768594796406303</v>
+        <v>7.899159917083225</v>
       </c>
       <c r="J82" t="n">
         <v>14</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.889999866485596</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I83" t="n">
-        <v>3.395585815510971</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J83" t="n">
         <v>14</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>22.89999961853027</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="I84" t="n">
-        <v>4.366812299816886</v>
+        <v>4.374453076554931</v>
       </c>
       <c r="J84" t="n">
         <v>14</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4.860000133514404</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="I85" t="n">
-        <v>4.423868191224254</v>
+        <v>4.574468270746932</v>
       </c>
       <c r="J85" t="n">
         <v>14</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>23.91500091552734</v>
+        <v>23.89500045776367</v>
       </c>
       <c r="I86" t="n">
-        <v>1.12899849326243</v>
+        <v>1.129943481178193</v>
       </c>
       <c r="J86" t="n">
         <v>14</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8.439999580383301</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I87" t="n">
-        <v>2.369668364259765</v>
+        <v>2.409638498843124</v>
       </c>
       <c r="J87" t="n">
         <v>14</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>9.359999656677246</v>
+        <v>9.265000343322754</v>
       </c>
       <c r="I88" t="n">
-        <v>2.564102658153289</v>
+        <v>2.590393859758105</v>
       </c>
       <c r="J88" t="n">
         <v>14</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>20.95000076293945</v>
+        <v>20.77000045776367</v>
       </c>
       <c r="I89" t="n">
-        <v>3.770882917567764</v>
+        <v>3.803562747177041</v>
       </c>
       <c r="J89" t="n">
         <v>14</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.139999866485596</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I90" t="n">
-        <v>1.80933856839937</v>
+        <v>1.845238109204414</v>
       </c>
       <c r="J90" t="n">
         <v>14</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>6.25</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I91" t="n">
-        <v>0.96</v>
+        <v>0.9756097409688789</v>
       </c>
       <c r="J91" t="n">
         <v>14</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>35.61999893188477</v>
+        <v>35.38000106811523</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9825940777519286</v>
+        <v>0.9892594387607948</v>
       </c>
       <c r="J92" t="n">
         <v>14</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.275000095367432</v>
+        <v>7.375</v>
       </c>
       <c r="I93" t="n">
-        <v>7.619243886374197</v>
+        <v>7.515932203389831</v>
       </c>
       <c r="J93" t="n">
         <v>14</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2.279999971389771</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I94" t="n">
-        <v>2.631578980390385</v>
+        <v>2.690582936628342</v>
       </c>
       <c r="J94" t="n">
         <v>14</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>12.60000038146973</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I95" t="n">
-        <v>1.587301539245438</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J95" t="n">
         <v>14</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.210000038146973</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="I96" t="n">
-        <v>1.658615126687416</v>
+        <v>1.696869803741844</v>
       </c>
       <c r="J96" t="n">
         <v>14</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.728000164031982</v>
+        <v>5.625</v>
       </c>
       <c r="I97" t="n">
-        <v>3.317039011155642</v>
+        <v>3.377777777777778</v>
       </c>
       <c r="J97" t="n">
         <v>14</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.10499954223633</v>
+        <v>10.06999969482422</v>
       </c>
       <c r="I98" t="n">
-        <v>4.275111524689831</v>
+        <v>4.289970338549658</v>
       </c>
       <c r="J98" t="n">
         <v>14</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>24.76000022888184</v>
+        <v>24.65999984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>1.777059757401587</v>
+        <v>1.784266028883106</v>
       </c>
       <c r="J99" t="n">
         <v>14</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8.670000076293945</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="I101" t="n">
-        <v>5.420991878478794</v>
+        <v>5.588585119233104</v>
       </c>
       <c r="J101" t="n">
         <v>14</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>52.18000030517578</v>
+        <v>51.08000183105469</v>
       </c>
       <c r="I102" t="n">
-        <v>2.683020298604967</v>
+        <v>2.740798648814561</v>
       </c>
       <c r="J102" t="n">
         <v>14</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.214000225067139</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="I103" t="n">
-        <v>7.11912634022748</v>
+        <v>7.211538726056125</v>
       </c>
       <c r="J103" t="n">
         <v>14</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3.490000009536743</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I105" t="n">
-        <v>4.871060158609155</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J105" t="n">
         <v>14</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.539999961853027</v>
+        <v>2.5</v>
       </c>
       <c r="I107" t="n">
-        <v>1.377952776600286</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>14</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.130000114440918</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I108" t="n">
-        <v>5.383360421520929</v>
+        <v>5.409836150151177</v>
       </c>
       <c r="J108" t="n">
         <v>14</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9589999914169312</v>
+        <v>0.9570000171661377</v>
       </c>
       <c r="I109" t="n">
-        <v>7.299270138321312</v>
+        <v>7.314524424699965</v>
       </c>
       <c r="J109" t="n">
         <v>14</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.41999816894531</v>
+        <v>49.88000106811523</v>
       </c>
       <c r="I110" t="n">
-        <v>1.43666537091487</v>
+        <v>1.423416168396702</v>
       </c>
       <c r="J110" t="n">
         <v>14</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>95.84999847412109</v>
+        <v>97.5</v>
       </c>
       <c r="I111" t="n">
-        <v>1.408450726647108</v>
+        <v>1.384615384615385</v>
       </c>
       <c r="J111" t="n">
         <v>14</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7.179999828338623</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I112" t="n">
-        <v>1.114206154772446</v>
+        <v>1.136363642521141</v>
       </c>
       <c r="J112" t="n">
         <v>14</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>4.666999816894531</v>
+        <v>4.644999980926514</v>
       </c>
       <c r="I114" t="n">
-        <v>3.642597100274148</v>
+        <v>3.659849315351149</v>
       </c>
       <c r="J114" t="n">
         <v>14</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>7.550000190734863</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I115" t="n">
-        <v>3.933774735058545</v>
+        <v>4.013513461789396</v>
       </c>
       <c r="J115" t="n">
         <v>14</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>57.5</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="I116" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.8021390592507499</v>
       </c>
       <c r="J116" t="n">
         <v>14</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>5.079999923706055</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7874015866287349</v>
+        <v>0.8130081174740657</v>
       </c>
       <c r="J117" t="n">
         <v>14</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.7599983215332</v>
+        <v>32.95999908447266</v>
       </c>
       <c r="I118" t="n">
-        <v>3.110189728090942</v>
+        <v>3.185679700138862</v>
       </c>
       <c r="J118" t="n">
         <v>14</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>20.29999923706055</v>
+        <v>19.79000091552734</v>
       </c>
       <c r="I120" t="n">
-        <v>1.871921252618846</v>
+        <v>1.92016160899644</v>
       </c>
       <c r="J120" t="n">
         <v>14</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>26.85000038146973</v>
+        <v>26.71999931335449</v>
       </c>
       <c r="I121" t="n">
-        <v>2.234636839759914</v>
+        <v>2.245509039740595</v>
       </c>
       <c r="J121" t="n">
         <v>14</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>33.25</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="I122" t="n">
-        <v>1.052631578947368</v>
+        <v>1.017441815334506</v>
       </c>
       <c r="J122" t="n">
         <v>14</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>3.599999904632568</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4722222347318393</v>
+        <v>0.4696132745146338</v>
       </c>
       <c r="J123" t="n">
         <v>14</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.835000038146973</v>
+        <v>2.884999990463257</v>
       </c>
       <c r="I124" t="n">
-        <v>0.352733681320733</v>
+        <v>0.3466204517523849</v>
       </c>
       <c r="J124" t="n">
         <v>14</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>21.88999938964844</v>
+        <v>21.38999938964844</v>
       </c>
       <c r="I125" t="n">
-        <v>5.116491691313783</v>
+        <v>5.236091781012473</v>
       </c>
       <c r="J125" t="n">
         <v>14</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>8.659999847412109</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9353348894596741</v>
+        <v>0.920454525504231</v>
       </c>
       <c r="J127" t="n">
         <v>14</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.125999927520752</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>4.341486507369556</v>
+        <v>4.176470516144929</v>
       </c>
       <c r="J128" t="n">
         <v>14</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.300000190734863</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I129" t="n">
-        <v>3.763440783030176</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J129" t="n">
         <v>7</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5.349999904632568</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I130" t="n">
-        <v>1.794392555350768</v>
+        <v>1.811320689531697</v>
       </c>
       <c r="J130" t="n">
         <v>7</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>12.10000038146973</v>
+        <v>12</v>
       </c>
       <c r="I132" t="n">
-        <v>1.652892509873682</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J132" t="n">
         <v>7</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.5</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="I133" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6224066168375152</v>
       </c>
       <c r="J133" t="n">
         <v>7</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>19.97999954223633</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="I134" t="n">
-        <v>2.502502559837576</v>
+        <v>2.493765680927293</v>
       </c>
       <c r="J134" t="n">
         <v>7</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.299999952316284</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I135" t="n">
-        <v>2.608695706257524</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J135" t="n">
         <v>7</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>16.6200008392334</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="I136" t="n">
-        <v>3.008423434129397</v>
+        <v>3.067484806153692</v>
       </c>
       <c r="J136" t="n">
         <v>7</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4.019999980926514</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I137" t="n">
-        <v>2.487562200857334</v>
+        <v>2.512562802029314</v>
       </c>
       <c r="J137" t="n">
         <v>7</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>3.650000095367432</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="I138" t="n">
-        <v>3.013698551394879</v>
+        <v>2.972972934658812</v>
       </c>
       <c r="J138" t="n">
         <v>7</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1.240000009536743</v>
+        <v>1.259999990463257</v>
       </c>
       <c r="I141" t="n">
-        <v>2.419354820102608</v>
+        <v>2.380952398973438</v>
       </c>
       <c r="J141" t="n">
         <v>7</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>7.099999904632568</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="I144" t="n">
-        <v>3.098591590916158</v>
+        <v>3.160919522905243</v>
       </c>
       <c r="J144" t="n">
         <v>7</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>27.45000076293945</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I145" t="n">
-        <v>2.222222160458253</v>
+        <v>2.226277403257571</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>11.60000038146973</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="I147" t="n">
-        <v>6.034482560174792</v>
+        <v>6.060605960522177</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>8.710000038146973</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="I148" t="n">
-        <v>5.86107919361855</v>
+        <v>6.121103005514844</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7.934999942779541</v>
+        <v>7.954999923706055</v>
       </c>
       <c r="I149" t="n">
-        <v>3.402646527372526</v>
+        <v>3.394091798736475</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>5.630000114440918</v>
+        <v>5.514999866485596</v>
       </c>
       <c r="I150" t="n">
-        <v>6.216696143615557</v>
+        <v>6.346328349469854</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.10000038146973</v>
+        <v>18</v>
       </c>
       <c r="I152" t="n">
-        <v>4.143646321509634</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.19999980926514</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I153" t="n">
-        <v>3.839285779668362</v>
+        <v>3.788546128174832</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>4.110000133514404</v>
+        <v>3.994999885559082</v>
       </c>
       <c r="I154" t="n">
-        <v>3.649634917937024</v>
+        <v>3.754693474265473</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>12.11999988555908</v>
+        <v>12.35999965667725</v>
       </c>
       <c r="I155" t="n">
-        <v>1.626806946053901</v>
+        <v>1.595218490912201</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>28.39999961853027</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="I156" t="n">
-        <v>3.873239488645198</v>
+        <v>3.992740582439903</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>55.20000076293945</v>
+        <v>54.59999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8514492635941262</v>
+        <v>0.8608058848623725</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>78.90000152587891</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="I158" t="n">
-        <v>1.520912518114977</v>
+        <v>1.505646230801351</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>25.5</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="I159" t="n">
-        <v>1.058823529411765</v>
+        <v>1.046511658853684</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>10.10000038146973</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I160" t="n">
-        <v>3.762376095521527</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>0.1889999955892563</v>
+        <v>0.183799996972084</v>
       </c>
       <c r="I162" t="n">
-        <v>3.703703790138033</v>
+        <v>3.808487549139175</v>
       </c>
       <c r="J162" t="n">
         <v>-7</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.309999942779541</v>
+        <v>7.420000076293945</v>
       </c>
       <c r="I163" t="n">
-        <v>2.188782506873206</v>
+        <v>2.156334209634064</v>
       </c>
       <c r="J163" t="n">
         <v>-7</v>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>2.154999971389771</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I164" t="n">
-        <v>3.016241339348193</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J164" t="n">
         <v>-7</v>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7.5</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="I165" t="n">
-        <v>3.333333333333333</v>
+        <v>3.410641236045195</v>
       </c>
       <c r="J165" t="n">
         <v>-7</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.639999866485596</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>7.530120633340297</v>
+        <v>7.309941357396413</v>
       </c>
       <c r="J167" t="n">
         <v>-14</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>18.5049991607666</v>
+        <v>18.2549991607666</v>
       </c>
       <c r="I168" t="n">
-        <v>3.512564331146247</v>
+        <v>3.560668473745928</v>
       </c>
       <c r="J168" t="n">
         <v>-14</v>
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>12.21000003814697</v>
+        <v>12.14500045776367</v>
       </c>
       <c r="I169" t="n">
-        <v>4.422604408787144</v>
+        <v>4.446274019321308</v>
       </c>
       <c r="J169" t="n">
         <v>-14</v>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>6.335999965667725</v>
+        <v>6.23799991607666</v>
       </c>
       <c r="I170" t="n">
-        <v>1.578282836834918</v>
+        <v>1.603077931153519</v>
       </c>
       <c r="J170" t="n">
         <v>-14</v>
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>9.340000152587891</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I171" t="n">
-        <v>1.713062070514719</v>
+        <v>1.716738253638083</v>
       </c>
       <c r="J171" t="n">
         <v>-14</v>
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>291.6499938964844</v>
+        <v>291.0499877929688</v>
       </c>
       <c r="I172" t="n">
-        <v>1.23949942590538</v>
+        <v>1.242054681882152</v>
       </c>
       <c r="J172" t="n">
         <v>-14</v>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>30.5</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="I173" t="n">
-        <v>4.459016393442623</v>
+        <v>4.473684266663655</v>
       </c>
       <c r="J173" t="n">
         <v>-14</v>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>13.96000003814697</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="I174" t="n">
-        <v>41.7020056167045</v>
+        <v>41.7319002121669</v>
       </c>
       <c r="J174" t="n">
         <v>-14</v>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>15.67000007629395</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="I175" t="n">
-        <v>3.73324822687784</v>
+        <v>3.803641064025216</v>
       </c>
       <c r="J175" t="n">
         <v>-14</v>
@@ -8693,10 +8693,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>19.79999923706055</v>
+        <v>19.5</v>
       </c>
       <c r="I176" t="n">
-        <v>3.181818304420946</v>
+        <v>3.230769230769231</v>
       </c>
       <c r="J176" t="n">
         <v>-14</v>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>129.0500030517578</v>
+        <v>126.3000030517578</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6974040904431741</v>
+        <v>0.7125890564160791</v>
       </c>
       <c r="J177" t="n">
         <v>-14</v>
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>65.29000091552734</v>
+        <v>64.05999755859375</v>
       </c>
       <c r="I178" t="n">
-        <v>2.63562563312931</v>
+        <v>2.686231760196426</v>
       </c>
       <c r="J178" t="n">
         <v>-14</v>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>26.39999961853027</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5303030379657029</v>
+        <v>0.5323194070770905</v>
       </c>
       <c r="J179" t="n">
         <v>-21</v>
@@ -8881,10 +8881,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1.529999971389771</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I180" t="n">
-        <v>3.92156870078234</v>
+        <v>3.947368470585578</v>
       </c>
       <c r="J180" t="n">
         <v>-21</v>
@@ -9352,7 +9352,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9532,14 +9532,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9556,7 +9556,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9566,14 +9566,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9590,7 +9590,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9607,7 +9607,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9617,14 +9617,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9634,14 +9634,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9651,14 +9651,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9668,14 +9668,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9685,14 +9685,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9726,7 +9726,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9736,14 +9736,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9753,14 +9753,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9770,14 +9770,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9794,7 +9794,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9811,7 +9811,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9981,7 +9981,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10008,14 +10008,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10042,14 +10042,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10059,14 +10059,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10093,14 +10093,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10110,14 +10110,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10144,14 +10144,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10168,7 +10168,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10185,7 +10185,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10202,7 +10202,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10212,14 +10212,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10236,7 +10236,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10246,14 +10246,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10270,7 +10270,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10287,7 +10287,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10304,7 +10304,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10331,14 +10331,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10355,7 +10355,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10382,14 +10382,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10440,7 +10440,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10474,7 +10474,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10484,14 +10484,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10501,14 +10501,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10518,14 +10518,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10535,14 +10535,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10627,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10722,14 +10722,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10739,14 +10739,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10756,14 +10756,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10780,7 +10780,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10797,7 +10797,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10814,7 +10814,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10824,14 +10824,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10841,14 +10841,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10865,7 +10865,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10892,14 +10892,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10916,7 +10916,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10933,7 +10933,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10950,7 +10950,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10967,7 +10967,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10984,7 +10984,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11001,7 +11001,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11018,7 +11018,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11028,14 +11028,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11052,7 +11052,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11062,14 +11062,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11079,14 +11079,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11096,14 +11096,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11130,14 +11130,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11147,14 +11147,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11171,7 +11171,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11188,7 +11188,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11232,14 +11232,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11256,7 +11256,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11266,14 +11266,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11290,7 +11290,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11307,7 +11307,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11324,7 +11324,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11334,14 +11334,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11351,14 +11351,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11375,7 +11375,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11392,7 +11392,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11402,14 +11402,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11426,7 +11426,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11443,7 +11443,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11453,14 +11453,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11477,7 +11477,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11494,7 +11494,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11511,7 +11511,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11521,14 +11521,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11545,7 +11545,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11596,7 +11596,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11606,14 +11606,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11630,7 +11630,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11647,7 +11647,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11657,14 +11657,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11674,14 +11674,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11698,7 +11698,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11715,7 +11715,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11725,14 +11725,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11742,14 +11742,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11776,14 +11776,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11793,14 +11793,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11817,7 +11817,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11844,14 +11844,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11861,14 +11861,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11885,7 +11885,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11919,7 +11919,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11936,7 +11936,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11946,14 +11946,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11963,14 +11963,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11980,14 +11980,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11997,14 +11997,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12014,14 +12014,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12055,7 +12055,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12072,7 +12072,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12089,7 +12089,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12106,7 +12106,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12140,7 +12140,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12150,14 +12150,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12174,7 +12174,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12184,14 +12184,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12201,14 +12201,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12218,14 +12218,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12235,14 +12235,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12259,7 +12259,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12276,7 +12276,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12310,7 +12310,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12320,14 +12320,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12337,14 +12337,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12361,7 +12361,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12378,7 +12378,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12395,7 +12395,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12405,14 +12405,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12429,7 +12429,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12439,14 +12439,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12456,14 +12456,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12473,14 +12473,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12497,7 +12497,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12514,7 +12514,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12531,7 +12531,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12558,14 +12558,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12575,14 +12575,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12599,7 +12599,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12609,14 +12609,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12633,7 +12633,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12643,14 +12643,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12667,7 +12667,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12684,7 +12684,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12701,7 +12701,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12718,7 +12718,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12728,14 +12728,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12745,14 +12745,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12762,14 +12762,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12779,14 +12779,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12803,7 +12803,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12820,7 +12820,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12830,14 +12830,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12871,7 +12871,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12881,14 +12881,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12898,14 +12898,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12949,14 +12949,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12973,7 +12973,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12990,7 +12990,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13000,14 +13000,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13034,14 +13034,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13051,14 +13051,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13068,14 +13068,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13085,14 +13085,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13102,14 +13102,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13119,14 +13119,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13136,14 +13136,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13153,14 +13153,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13177,7 +13177,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13194,7 +13194,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13204,14 +13204,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13221,14 +13221,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13245,7 +13245,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13255,14 +13255,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13272,14 +13272,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13296,7 +13296,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13306,14 +13306,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13323,14 +13323,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13340,14 +13340,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13357,14 +13357,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13381,7 +13381,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13415,7 +13415,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13466,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13476,14 +13476,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13493,14 +13493,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13510,14 +13510,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13527,14 +13527,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13544,14 +13544,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13619,7 +13619,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13629,14 +13629,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13670,7 +13670,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13680,14 +13680,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13697,14 +13697,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13714,14 +13714,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13731,14 +13731,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13755,7 +13755,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13765,14 +13765,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13782,14 +13782,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13806,7 +13806,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13840,7 +13840,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13850,14 +13850,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13874,7 +13874,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13891,7 +13891,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13908,7 +13908,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13993,7 +13993,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14003,14 +14003,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14061,7 +14061,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14078,7 +14078,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14095,7 +14095,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14105,14 +14105,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14122,14 +14122,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14163,7 +14163,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14180,7 +14180,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14190,14 +14190,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14224,14 +14224,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14248,7 +14248,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14265,7 +14265,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14275,14 +14275,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14292,14 +14292,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14309,14 +14309,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14326,14 +14326,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14350,7 +14350,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14360,14 +14360,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14377,14 +14377,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14401,7 +14401,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14411,14 +14411,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14428,14 +14428,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14452,7 +14452,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14462,14 +14462,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14479,14 +14479,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14496,14 +14496,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14513,14 +14513,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14537,7 +14537,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14554,7 +14554,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14564,14 +14564,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14588,7 +14588,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14598,14 +14598,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14622,7 +14622,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14639,7 +14639,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14649,14 +14649,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14666,14 +14666,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14683,14 +14683,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14741,7 +14741,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14779,78 +14779,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CULTI Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>